--- a/Excel/Shared/Item.xlsx
+++ b/Excel/Shared/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>icon_hammer</t>
+          <t>item_hammer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>icon_row</t>
+          <t>item_rocket_h</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>icon_col</t>
+          <t>item_rocket_v</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>icon_bomb3</t>
+          <t>item_flower_5col</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>icon_shuffle</t>
+          <t>item_score_20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -639,12 +639,124 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>icon_steps</t>
+          <t>item_steps_3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>本局额外增加步数</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>item_gold</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>货币：金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>体力</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>item_energy_10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>恢复体力</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>item_diamond</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>货币：钻石</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>加分</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>item_score_20</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>额外分数</t>
         </is>
       </c>
     </row>
